--- a/data/industry/CFM/UDIMM.xlsx
+++ b/data/industry/CFM/UDIMM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6393E40F-7B17-4CFB-86CF-8FA32BE1C378}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1297D31F-E806-4637-B1B4-2E30520E19B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 UDIMM 8GB 3200" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -138,7 +138,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -176,6 +176,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -457,15 +464,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="11"/>
+    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -482,13 +489,13 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
@@ -505,13 +512,13 @@
       <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="10">
         <v>13.5</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="10">
         <v>20.3</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="10">
         <v>15.5</v>
       </c>
     </row>
@@ -528,13 +535,13 @@
       <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="10">
         <v>13.5</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="10">
         <v>20.3</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="10">
         <v>15.5</v>
       </c>
     </row>
@@ -551,13 +558,13 @@
       <c r="D4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="10">
         <v>12</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="10">
         <v>18.8</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="10">
         <v>14</v>
       </c>
     </row>
@@ -574,13 +581,13 @@
       <c r="D5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="10">
         <v>12</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="10">
         <v>18.8</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="10">
         <v>14</v>
       </c>
     </row>
@@ -597,13 +604,13 @@
       <c r="D6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="10">
         <v>12</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="10">
         <v>18.8</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="10">
         <v>14</v>
       </c>
     </row>
@@ -620,13 +627,13 @@
       <c r="D7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="10">
         <v>12.5</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="10">
         <v>19.3</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="10">
         <v>14.5</v>
       </c>
     </row>
@@ -643,13 +650,13 @@
       <c r="D8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="10">
         <v>12.5</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="10">
         <v>19.3</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="10">
         <v>14.5</v>
       </c>
     </row>
@@ -666,13 +673,13 @@
       <c r="D9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="10">
         <v>12.8</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="10">
         <v>19.600000000000001</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="10">
         <v>14.8</v>
       </c>
     </row>
@@ -689,13 +696,13 @@
       <c r="D10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="10">
         <v>13</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="10">
         <v>19.8</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="10">
         <v>15</v>
       </c>
     </row>
@@ -712,13 +719,13 @@
       <c r="D11" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="10">
         <v>13</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="10">
         <v>19.8</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="10">
         <v>15</v>
       </c>
     </row>
@@ -735,13 +742,13 @@
       <c r="D12" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="10">
         <v>13</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="10">
         <v>19.8</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="10">
         <v>15</v>
       </c>
     </row>
@@ -758,13 +765,13 @@
       <c r="D13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="10">
         <v>15</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="10">
         <v>21.8</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="10">
         <v>17</v>
       </c>
     </row>
@@ -781,13 +788,13 @@
       <c r="D14" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="10">
         <v>15</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="10">
         <v>21.8</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="10">
         <v>17</v>
       </c>
     </row>
@@ -804,13 +811,13 @@
       <c r="D15" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="10">
         <v>18</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="10">
         <v>24.8</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="10">
         <v>20</v>
       </c>
     </row>
@@ -827,13 +834,13 @@
       <c r="D16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="10">
         <v>18</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="10">
         <v>24.8</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="10">
         <v>20</v>
       </c>
     </row>
@@ -850,13 +857,13 @@
       <c r="D17" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="10">
         <v>18</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="10">
         <v>24.8</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="10">
         <v>20</v>
       </c>
     </row>
@@ -873,13 +880,13 @@
       <c r="D18" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="10">
         <v>22</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="10">
         <v>28.8</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="10">
         <v>24</v>
       </c>
     </row>
@@ -896,13 +903,13 @@
       <c r="D19" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="10">
         <v>28</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="10">
         <v>34.799999999999997</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="10">
         <v>30</v>
       </c>
     </row>
@@ -919,13 +926,13 @@
       <c r="D20" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="10">
         <v>32</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="10">
         <v>38.799999999999997</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="10">
         <v>34</v>
       </c>
     </row>
@@ -942,13 +949,13 @@
       <c r="D21" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="10">
         <v>36</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="10">
         <v>42.8</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="10">
         <v>38</v>
       </c>
     </row>
@@ -965,13 +972,13 @@
       <c r="D22" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="10">
         <v>36</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="10">
         <v>42.8</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="10">
         <v>38</v>
       </c>
     </row>
@@ -988,13 +995,13 @@
       <c r="D23" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="10">
         <v>36</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="10">
         <v>42.8</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="10">
         <v>38</v>
       </c>
     </row>
@@ -1011,13 +1018,13 @@
       <c r="D24" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="10">
         <v>36</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="10">
         <v>42.8</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="10">
         <v>38</v>
       </c>
     </row>
@@ -1034,13 +1041,13 @@
       <c r="D25" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="10">
         <v>43</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="10">
         <v>50</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="10">
         <v>45</v>
       </c>
     </row>
@@ -1057,13 +1064,13 @@
       <c r="D26" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="10">
         <v>43</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="10">
         <v>50</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="10">
         <v>45</v>
       </c>
     </row>
@@ -1080,13 +1087,13 @@
       <c r="D27" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="10">
         <v>45</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="10">
         <v>52</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="10">
         <v>47</v>
       </c>
     </row>
@@ -1103,13 +1110,13 @@
       <c r="D28" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="11">
         <v>48</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="11">
         <v>55</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="11">
         <v>50</v>
       </c>
     </row>
@@ -1126,13 +1133,13 @@
       <c r="D29" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="11">
         <v>48</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="11">
         <v>55</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="11">
         <v>50</v>
       </c>
     </row>
@@ -1149,13 +1156,13 @@
       <c r="D30" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="11">
         <v>48</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="11">
         <v>55</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="11">
         <v>50</v>
       </c>
     </row>
@@ -1172,13 +1179,13 @@
       <c r="D31" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="11">
         <v>48</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="11">
         <v>55</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="11">
         <v>50</v>
       </c>
     </row>
@@ -1195,13 +1202,13 @@
       <c r="D32" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="11">
         <v>48</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="11">
         <v>55</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="11">
         <v>50</v>
       </c>
     </row>
@@ -1218,13 +1225,13 @@
       <c r="D33" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="11">
         <v>58</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="11">
         <v>65</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="11">
         <v>60</v>
       </c>
     </row>
@@ -1241,13 +1248,13 @@
       <c r="D34" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="11">
         <v>58</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="11">
         <v>65</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="11">
         <v>60</v>
       </c>
     </row>
@@ -1264,14 +1271,106 @@
       <c r="D35" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="11">
         <v>58</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="11">
         <v>65</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="11">
         <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="11">
+        <v>43</v>
+      </c>
+      <c r="F36" s="11">
+        <v>50</v>
+      </c>
+      <c r="G36" s="11">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="11">
+        <v>43</v>
+      </c>
+      <c r="F37" s="11">
+        <v>50</v>
+      </c>
+      <c r="G37" s="11">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="11">
+        <v>42</v>
+      </c>
+      <c r="F38" s="11">
+        <v>49</v>
+      </c>
+      <c r="G38" s="11">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.45833333333333098</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="11">
+        <v>40</v>
+      </c>
+      <c r="F39" s="11">
+        <v>47</v>
+      </c>
+      <c r="G39" s="11">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1282,15 +1381,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192B0709-717A-492E-9744-92D2DEF39476}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="11" customWidth="1"/>
+    <col min="6" max="6" width="9" style="11"/>
+    <col min="7" max="7" width="11.19921875" style="11" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1307,13 +1407,13 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1330,13 +1430,13 @@
       <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="10">
         <v>26</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="10">
         <v>37.6</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="10">
         <v>27</v>
       </c>
     </row>
@@ -1353,13 +1453,13 @@
       <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="10">
         <v>26</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="10">
         <v>37.6</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="10">
         <v>27</v>
       </c>
     </row>
@@ -1376,13 +1476,13 @@
       <c r="D4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="10">
         <v>25</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="10">
         <v>36.6</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="10">
         <v>26</v>
       </c>
     </row>
@@ -1399,13 +1499,13 @@
       <c r="D5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="10">
         <v>25</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="10">
         <v>36.6</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="10">
         <v>26</v>
       </c>
     </row>
@@ -1422,13 +1522,13 @@
       <c r="D6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="10">
         <v>25</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="10">
         <v>36.6</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="10">
         <v>26</v>
       </c>
     </row>
@@ -1445,13 +1545,13 @@
       <c r="D7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="10">
         <v>25.5</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="10">
         <v>37.1</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="10">
         <v>26.5</v>
       </c>
     </row>
@@ -1468,13 +1568,13 @@
       <c r="D8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="10">
         <v>25.5</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="10">
         <v>37.1</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="10">
         <v>26.5</v>
       </c>
     </row>
@@ -1491,13 +1591,13 @@
       <c r="D9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="10">
         <v>25.8</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="10">
         <v>37.4</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="10">
         <v>26.8</v>
       </c>
     </row>
@@ -1514,13 +1614,13 @@
       <c r="D10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="10">
         <v>26</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="10">
         <v>37.6</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="10">
         <v>27</v>
       </c>
     </row>
@@ -1537,13 +1637,13 @@
       <c r="D11" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="10">
         <v>26</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="10">
         <v>37.6</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="10">
         <v>27</v>
       </c>
     </row>
@@ -1560,13 +1660,13 @@
       <c r="D12" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="10">
         <v>26</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="10">
         <v>37.6</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="10">
         <v>27</v>
       </c>
     </row>
@@ -1583,13 +1683,13 @@
       <c r="D13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="10">
         <v>30</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="10">
         <v>41.6</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="10">
         <v>31</v>
       </c>
     </row>
@@ -1606,13 +1706,13 @@
       <c r="D14" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="10">
         <v>30</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="10">
         <v>41.6</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="10">
         <v>31</v>
       </c>
     </row>
@@ -1629,13 +1729,13 @@
       <c r="D15" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="10">
         <v>35</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="10">
         <v>46.6</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="10">
         <v>36</v>
       </c>
     </row>
@@ -1652,13 +1752,13 @@
       <c r="D16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="10">
         <v>35</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="10">
         <v>46.6</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="10">
         <v>36</v>
       </c>
     </row>
@@ -1675,13 +1775,13 @@
       <c r="D17" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="10">
         <v>35</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="10">
         <v>46.6</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="10">
         <v>36</v>
       </c>
     </row>
@@ -1698,13 +1798,13 @@
       <c r="D18" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="10">
         <v>44</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="10">
         <v>55.6</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="10">
         <v>45</v>
       </c>
     </row>
@@ -1721,13 +1821,13 @@
       <c r="D19" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="10">
         <v>54</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="10">
         <v>65.599999999999994</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="10">
         <v>55</v>
       </c>
     </row>
@@ -1744,13 +1844,13 @@
       <c r="D20" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="10">
         <v>59</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="10">
         <v>70.599999999999994</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="10">
         <v>60</v>
       </c>
     </row>
@@ -1767,13 +1867,13 @@
       <c r="D21" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="10">
         <v>74</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="10">
         <v>85.6</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="10">
         <v>75</v>
       </c>
     </row>
@@ -1790,13 +1890,13 @@
       <c r="D22" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="10">
         <v>74</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="10">
         <v>85.6</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="10">
         <v>75</v>
       </c>
     </row>
@@ -1813,13 +1913,13 @@
       <c r="D23" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="10">
         <v>74</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="10">
         <v>85.6</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="10">
         <v>75</v>
       </c>
     </row>
@@ -1836,13 +1936,13 @@
       <c r="D24" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="10">
         <v>74</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="10">
         <v>85.6</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="10">
         <v>75</v>
       </c>
     </row>
@@ -1859,13 +1959,13 @@
       <c r="D25" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="10">
         <v>84</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="10">
         <v>95.6</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="10">
         <v>85</v>
       </c>
     </row>
@@ -1882,13 +1982,13 @@
       <c r="D26" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="10">
         <v>84</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="10">
         <v>95.6</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="10">
         <v>85</v>
       </c>
     </row>
@@ -1905,13 +2005,13 @@
       <c r="D27" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="10">
         <v>89</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="10">
         <v>100.6</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="10">
         <v>90</v>
       </c>
     </row>
@@ -1928,13 +2028,13 @@
       <c r="D28" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="11">
         <v>94</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="11">
         <v>105.6</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="11">
         <v>95</v>
       </c>
     </row>
@@ -1951,13 +2051,13 @@
       <c r="D29" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="11">
         <v>94</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="11">
         <v>105.6</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="11">
         <v>95</v>
       </c>
     </row>
@@ -1974,13 +2074,13 @@
       <c r="D30" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="11">
         <v>94</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="11">
         <v>105.6</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="11">
         <v>95</v>
       </c>
     </row>
@@ -1997,13 +2097,13 @@
       <c r="D31" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="11">
         <v>94</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="11">
         <v>105.6</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="11">
         <v>95</v>
       </c>
     </row>
@@ -2020,13 +2120,13 @@
       <c r="D32" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="11">
         <v>94</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="11">
         <v>105.6</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="11">
         <v>95</v>
       </c>
     </row>
@@ -2043,13 +2143,13 @@
       <c r="D33" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="11">
         <v>119</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="11">
         <v>130.6</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="11">
         <v>120</v>
       </c>
     </row>
@@ -2066,13 +2166,13 @@
       <c r="D34" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="11">
         <v>119</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="11">
         <v>130.6</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="11">
         <v>120</v>
       </c>
     </row>
@@ -2089,14 +2189,106 @@
       <c r="D35" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="11">
         <v>119</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="11">
         <v>130.6</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="11">
         <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="11">
+        <v>89</v>
+      </c>
+      <c r="F36" s="11">
+        <v>100</v>
+      </c>
+      <c r="G36" s="11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="11">
+        <v>89</v>
+      </c>
+      <c r="F37" s="11">
+        <v>100</v>
+      </c>
+      <c r="G37" s="11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="11">
+        <v>84</v>
+      </c>
+      <c r="F38" s="11">
+        <v>95</v>
+      </c>
+      <c r="G38" s="11">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.45833333333333098</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="11">
+        <v>84</v>
+      </c>
+      <c r="F39" s="11">
+        <v>95</v>
+      </c>
+      <c r="G39" s="11">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2107,15 +2299,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C33C41F-CAF1-4FD5-8D91-A49D334C85A7}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -2922,6 +3114,98 @@
       </c>
       <c r="G35" s="14">
         <v>220</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="14">
+        <v>195</v>
+      </c>
+      <c r="F36" s="14">
+        <v>210</v>
+      </c>
+      <c r="G36" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="14">
+        <v>195</v>
+      </c>
+      <c r="F37" s="14">
+        <v>210</v>
+      </c>
+      <c r="G37" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="14">
+        <v>175</v>
+      </c>
+      <c r="F38" s="14">
+        <v>190</v>
+      </c>
+      <c r="G38" s="14">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="14">
+        <v>170</v>
+      </c>
+      <c r="F39" s="14">
+        <v>185</v>
+      </c>
+      <c r="G39" s="14">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2932,15 +3216,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A33F9B6-7347-4C68-802E-E71624384C9E}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -3747,6 +4031,98 @@
       </c>
       <c r="G35" s="14">
         <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="14">
+        <v>168</v>
+      </c>
+      <c r="F36" s="14">
+        <v>172</v>
+      </c>
+      <c r="G36" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="14">
+        <v>168</v>
+      </c>
+      <c r="F37" s="14">
+        <v>172</v>
+      </c>
+      <c r="G37" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="14">
+        <v>163</v>
+      </c>
+      <c r="F38" s="14">
+        <v>167</v>
+      </c>
+      <c r="G38" s="14">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.45833333333333098</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="14">
+        <v>158</v>
+      </c>
+      <c r="F39" s="14">
+        <v>162</v>
+      </c>
+      <c r="G39" s="14">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -3757,15 +4133,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55494817-78A6-45DF-9F77-86066DAB20E2}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="17"/>
+    <col min="7" max="7" width="11.19921875" style="17" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -3782,13 +4158,13 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3805,13 +4181,13 @@
       <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="16">
         <v>33</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="16">
         <v>37</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="16">
         <v>35</v>
       </c>
     </row>
@@ -3828,13 +4204,13 @@
       <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="16">
         <v>33</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="16">
         <v>37</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="16">
         <v>35</v>
       </c>
     </row>
@@ -3851,13 +4227,13 @@
       <c r="D4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="16">
         <v>33</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="16">
         <v>37</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="16">
         <v>35</v>
       </c>
     </row>
@@ -3874,13 +4250,13 @@
       <c r="D5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="16">
         <v>33</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="16">
         <v>37</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="16">
         <v>35</v>
       </c>
     </row>
@@ -3897,13 +4273,13 @@
       <c r="D6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="16">
         <v>33</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="16">
         <v>37</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="16">
         <v>35</v>
       </c>
     </row>
@@ -3920,13 +4296,13 @@
       <c r="D7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="16">
         <v>34</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="16">
         <v>38</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="16">
         <v>36</v>
       </c>
     </row>
@@ -3943,13 +4319,13 @@
       <c r="D8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="16">
         <v>35</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="16">
         <v>39</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="16">
         <v>37</v>
       </c>
     </row>
@@ -3966,13 +4342,13 @@
       <c r="D9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="16">
         <v>35.4</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="16">
         <v>39.4</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="16">
         <v>37.4</v>
       </c>
     </row>
@@ -3989,13 +4365,13 @@
       <c r="D10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="16">
         <v>36</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="16">
         <v>40</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="16">
         <v>38</v>
       </c>
     </row>
@@ -4012,13 +4388,13 @@
       <c r="D11" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="16">
         <v>36</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="16">
         <v>40</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="16">
         <v>38</v>
       </c>
     </row>
@@ -4035,13 +4411,13 @@
       <c r="D12" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="16">
         <v>36</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="16">
         <v>40</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="16">
         <v>38</v>
       </c>
     </row>
@@ -4058,13 +4434,13 @@
       <c r="D13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="16">
         <v>43</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="16">
         <v>47</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="16">
         <v>45</v>
       </c>
     </row>
@@ -4081,13 +4457,13 @@
       <c r="D14" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="16">
         <v>43</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="16">
         <v>47</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="16">
         <v>45</v>
       </c>
     </row>
@@ -4104,13 +4480,13 @@
       <c r="D15" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="16">
         <v>43</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="16">
         <v>47</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="16">
         <v>45</v>
       </c>
     </row>
@@ -4127,13 +4503,13 @@
       <c r="D16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="16">
         <v>43</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="16">
         <v>47</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="16">
         <v>45</v>
       </c>
     </row>
@@ -4150,13 +4526,13 @@
       <c r="D17" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="16">
         <v>43</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="16">
         <v>47</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="16">
         <v>45</v>
       </c>
     </row>
@@ -4173,13 +4549,13 @@
       <c r="D18" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="16">
         <v>43</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="16">
         <v>47</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="16">
         <v>45</v>
       </c>
     </row>
@@ -4196,13 +4572,13 @@
       <c r="D19" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="16">
         <v>63</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="16">
         <v>67</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="16">
         <v>65</v>
       </c>
     </row>
@@ -4219,13 +4595,13 @@
       <c r="D20" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="16">
         <v>88</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="16">
         <v>92</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="16">
         <v>90</v>
       </c>
     </row>
@@ -4242,13 +4618,13 @@
       <c r="D21" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="16">
         <v>118</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="16">
         <v>122</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="16">
         <v>120</v>
       </c>
     </row>
@@ -4265,13 +4641,13 @@
       <c r="D22" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="16">
         <v>118</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="16">
         <v>122</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="16">
         <v>120</v>
       </c>
     </row>
@@ -4288,13 +4664,13 @@
       <c r="D23" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="16">
         <v>118</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="16">
         <v>122</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="16">
         <v>120</v>
       </c>
     </row>
@@ -4311,13 +4687,13 @@
       <c r="D24" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="16">
         <v>118</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="16">
         <v>122</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="16">
         <v>120</v>
       </c>
     </row>
@@ -4334,13 +4710,13 @@
       <c r="D25" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="16">
         <v>143</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="16">
         <v>147</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="16">
         <v>145</v>
       </c>
     </row>
@@ -4357,13 +4733,13 @@
       <c r="D26" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="16">
         <v>143</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="16">
         <v>147</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="16">
         <v>145</v>
       </c>
     </row>
@@ -4380,13 +4756,13 @@
       <c r="D27" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="16">
         <v>167</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="16">
         <v>172</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="16">
         <v>170</v>
       </c>
     </row>
@@ -4403,13 +4779,13 @@
       <c r="D28" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="17">
         <v>177</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="17">
         <v>182</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="17">
         <v>180</v>
       </c>
     </row>
@@ -4426,13 +4802,13 @@
       <c r="D29" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="17">
         <v>177</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="17">
         <v>182</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="17">
         <v>180</v>
       </c>
     </row>
@@ -4449,13 +4825,13 @@
       <c r="D30" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="17">
         <v>177</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="17">
         <v>182</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="17">
         <v>180</v>
       </c>
     </row>
@@ -4472,13 +4848,13 @@
       <c r="D31" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="17">
         <v>177</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="17">
         <v>182</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="17">
         <v>180</v>
       </c>
     </row>
@@ -4495,13 +4871,13 @@
       <c r="D32" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="17">
         <v>177</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="17">
         <v>182</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="17">
         <v>180</v>
       </c>
     </row>
@@ -4518,13 +4894,13 @@
       <c r="D33" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="17">
         <v>197</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="17">
         <v>202</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="17">
         <v>200</v>
       </c>
     </row>
@@ -4541,13 +4917,13 @@
       <c r="D34" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="17">
         <v>197</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="17">
         <v>202</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="17">
         <v>200</v>
       </c>
     </row>
@@ -4564,14 +4940,106 @@
       <c r="D35" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="17">
         <v>197</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="17">
         <v>202</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="17">
         <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="17">
+        <v>177</v>
+      </c>
+      <c r="F36" s="17">
+        <v>182</v>
+      </c>
+      <c r="G36" s="17">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="17">
+        <v>177</v>
+      </c>
+      <c r="F37" s="17">
+        <v>182</v>
+      </c>
+      <c r="G37" s="17">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="17">
+        <v>167</v>
+      </c>
+      <c r="F38" s="17">
+        <v>172</v>
+      </c>
+      <c r="G38" s="17">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.45833333333333098</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="17">
+        <v>164</v>
+      </c>
+      <c r="F39" s="17">
+        <v>169</v>
+      </c>
+      <c r="G39" s="17">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -4582,15 +5050,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B6A378-E9BB-4F97-B1F3-B76BB8A3CEFF}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.25" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -5397,6 +5865,98 @@
       </c>
       <c r="G35" s="11">
         <v>320</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="11">
+        <v>287</v>
+      </c>
+      <c r="F36" s="11">
+        <v>293</v>
+      </c>
+      <c r="G36" s="11">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="11">
+        <v>287</v>
+      </c>
+      <c r="F37" s="11">
+        <v>293</v>
+      </c>
+      <c r="G37" s="11">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="11">
+        <v>277</v>
+      </c>
+      <c r="F38" s="11">
+        <v>283</v>
+      </c>
+      <c r="G38" s="11">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.45833333333333098</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="11">
+        <v>272</v>
+      </c>
+      <c r="F39" s="11">
+        <v>278</v>
+      </c>
+      <c r="G39" s="11">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -5407,15 +5967,16 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D2BE078-281B-4EE8-A7DD-0530E85C5130}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.25" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.69921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="11"/>
+    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -6224,6 +6785,98 @@
         <v>330</v>
       </c>
     </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="11">
+        <v>297</v>
+      </c>
+      <c r="F36" s="11">
+        <v>303</v>
+      </c>
+      <c r="G36" s="11">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="11">
+        <v>297</v>
+      </c>
+      <c r="F37" s="11">
+        <v>303</v>
+      </c>
+      <c r="G37" s="11">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="11">
+        <v>287</v>
+      </c>
+      <c r="F38" s="11">
+        <v>293</v>
+      </c>
+      <c r="G38" s="11">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.45833333333333098</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="11">
+        <v>277</v>
+      </c>
+      <c r="F39" s="11">
+        <v>283</v>
+      </c>
+      <c r="G39" s="11">
+        <v>280</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/industry/CFM/UDIMM.xlsx
+++ b/data/industry/CFM/UDIMM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55B6EF2-E80D-4F9F-AAF2-5612D03481E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA32A55-D311-4655-B2F9-429D7B2739A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -81,7 +81,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,6 +124,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -148,7 +154,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -193,7 +199,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -203,23 +208,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -507,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -1554,6 +1559,75 @@
         <v>38</v>
       </c>
     </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="11">
+        <v>36</v>
+      </c>
+      <c r="F46" s="11">
+        <v>43</v>
+      </c>
+      <c r="G46" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="11">
+        <v>36</v>
+      </c>
+      <c r="F47" s="11">
+        <v>43</v>
+      </c>
+      <c r="G47" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="11">
+        <v>34</v>
+      </c>
+      <c r="F48" s="11">
+        <v>41</v>
+      </c>
+      <c r="G48" s="11">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1562,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192B0709-717A-492E-9744-92D2DEF39476}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -2610,6 +2684,75 @@
         <v>76</v>
       </c>
     </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="11">
+        <v>75</v>
+      </c>
+      <c r="F46" s="11">
+        <v>86</v>
+      </c>
+      <c r="G46" s="11">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="11">
+        <v>75</v>
+      </c>
+      <c r="F47" s="11">
+        <v>86</v>
+      </c>
+      <c r="G47" s="11">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="11">
+        <v>73</v>
+      </c>
+      <c r="F48" s="11">
+        <v>84</v>
+      </c>
+      <c r="G48" s="11">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2618,7 +2761,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C33C41F-CAF1-4FD5-8D91-A49D334C85A7}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -3665,6 +3808,75 @@
         <v>163</v>
       </c>
     </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="14">
+        <v>158</v>
+      </c>
+      <c r="F46" s="14">
+        <v>173</v>
+      </c>
+      <c r="G46" s="14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="14">
+        <v>158</v>
+      </c>
+      <c r="F47" s="14">
+        <v>173</v>
+      </c>
+      <c r="G47" s="14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="14">
+        <v>155</v>
+      </c>
+      <c r="F48" s="14">
+        <v>170</v>
+      </c>
+      <c r="G48" s="14">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3673,1319 +3885,1525 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{804C6E38-9512-4F25-B73E-A84B442434F8}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="26"/>
-    <col min="7" max="7" width="11.21875" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="18"/>
+    <col min="1" max="1" width="12.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="25"/>
+    <col min="7" max="7" width="11.21875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="23">
+      <c r="A2" s="22">
         <v>46161</v>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="22">
         <v>46161</v>
       </c>
-      <c r="C2" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="26">
+      <c r="C2" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="25">
         <v>70</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="25">
         <v>85</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="25">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="23">
+      <c r="A3" s="22">
         <v>46168</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="22">
         <v>46168</v>
       </c>
-      <c r="C3" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="26">
+      <c r="C3" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="25">
         <v>70</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="25">
         <v>85</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="25">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="23">
+      <c r="A4" s="22">
         <v>46175</v>
       </c>
-      <c r="B4" s="23">
+      <c r="B4" s="22">
         <v>46175</v>
       </c>
-      <c r="C4" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="26">
+      <c r="C4" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="25">
         <v>70</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="25">
         <v>85</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="25">
         <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="23">
+      <c r="A5" s="22">
         <v>46182</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="22">
         <v>46182</v>
       </c>
-      <c r="C5" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="26">
+      <c r="C5" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="25">
         <v>72</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="25">
         <v>87</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="25">
         <v>82</v>
       </c>
     </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="22">
+        <v>46189</v>
+      </c>
+      <c r="B6" s="22">
+        <v>46189</v>
+      </c>
+      <c r="C6" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="25">
+        <v>74</v>
+      </c>
+      <c r="F6" s="25">
+        <v>89</v>
+      </c>
+      <c r="G6" s="25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="22">
+        <v>46196</v>
+      </c>
+      <c r="B7" s="22">
+        <v>46196</v>
+      </c>
+      <c r="C7" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="25">
+        <v>74</v>
+      </c>
+      <c r="F7" s="25">
+        <v>89</v>
+      </c>
+      <c r="G7" s="25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="22">
+        <v>46203</v>
+      </c>
+      <c r="B8" s="22">
+        <v>46203</v>
+      </c>
+      <c r="C8" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="25">
+        <v>75</v>
+      </c>
+      <c r="F8" s="25">
+        <v>90</v>
+      </c>
+      <c r="G8" s="25">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04103911-DA80-4A49-87A1-FE7A2CF5D7A5}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.88671875" style="26"/>
-    <col min="7" max="7" width="11.21875" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="18"/>
+    <col min="1" max="1" width="12.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.88671875" style="25"/>
+    <col min="7" max="7" width="11.21875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="23">
+      <c r="A2" s="22">
         <v>46161</v>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="22">
         <v>46161</v>
       </c>
-      <c r="C2" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="26">
+      <c r="C2" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="25">
         <v>75</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="25">
         <v>90</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="25">
         <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="23">
+      <c r="A3" s="22">
         <v>46168</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="22">
         <v>46168</v>
       </c>
-      <c r="C3" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="26">
+      <c r="C3" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="25">
         <v>75</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="25">
         <v>90</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="25">
         <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="23">
+      <c r="A4" s="22">
         <v>46175</v>
       </c>
-      <c r="B4" s="23">
+      <c r="B4" s="22">
         <v>46175</v>
       </c>
-      <c r="C4" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="26">
+      <c r="C4" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="25">
         <v>75</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="25">
         <v>90</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="25">
         <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="23">
+      <c r="A5" s="22">
         <v>46182</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="22">
         <v>46182</v>
       </c>
-      <c r="C5" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="26">
+      <c r="C5" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="25">
         <v>77</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="25">
         <v>92</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="25">
         <v>87</v>
       </c>
     </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="22">
+        <v>46189</v>
+      </c>
+      <c r="B6" s="22">
+        <v>46189</v>
+      </c>
+      <c r="C6" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="25">
+        <v>79</v>
+      </c>
+      <c r="F6" s="25">
+        <v>94</v>
+      </c>
+      <c r="G6" s="25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="22">
+        <v>46196</v>
+      </c>
+      <c r="B7" s="22">
+        <v>46196</v>
+      </c>
+      <c r="C7" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="25">
+        <v>97</v>
+      </c>
+      <c r="F7" s="25">
+        <v>94</v>
+      </c>
+      <c r="G7" s="25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="22">
+        <v>46203</v>
+      </c>
+      <c r="B8" s="22">
+        <v>46203</v>
+      </c>
+      <c r="C8" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="25">
+        <v>80</v>
+      </c>
+      <c r="F8" s="25">
+        <v>95</v>
+      </c>
+      <c r="G8" s="25">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A33F9B6-7347-4C68-802E-E71624384C9E}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="30"/>
-    <col min="7" max="7" width="11.21875" style="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="18"/>
+    <col min="1" max="1" width="12.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="29"/>
+    <col min="7" max="7" width="11.21875" style="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="28">
+      <c r="A2" s="27">
         <v>45860</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="27">
         <v>45860</v>
       </c>
-      <c r="C2" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="29">
+      <c r="C2" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="28">
         <v>30</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="28">
         <v>34</v>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="28">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="28">
+      <c r="A3" s="27">
         <v>45867</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="27">
         <v>45867</v>
       </c>
-      <c r="C3" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="29">
+      <c r="C3" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="28">
         <v>30</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="28">
         <v>34</v>
       </c>
-      <c r="G3" s="29">
+      <c r="G3" s="28">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="28">
+      <c r="A4" s="27">
         <v>45874</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="27">
         <v>45874</v>
       </c>
-      <c r="C4" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="29">
+      <c r="C4" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="28">
         <v>30</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="28">
         <v>34</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="28">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="28">
+      <c r="A5" s="27">
         <v>45881</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>45881</v>
       </c>
-      <c r="C5" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="29">
+      <c r="C5" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="28">
         <v>30</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="28">
         <v>34</v>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="28">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="28">
+      <c r="A6" s="27">
         <v>45888</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="27">
         <v>45888</v>
       </c>
-      <c r="C6" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="29">
+      <c r="C6" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="28">
         <v>30</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="28">
         <v>34</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="28">
         <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="28">
+      <c r="A7" s="27">
         <v>45895</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <v>45895</v>
       </c>
-      <c r="C7" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="29">
+      <c r="C7" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="28">
         <v>31</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="28">
         <v>35</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="28">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="28">
+      <c r="A8" s="27">
         <v>45902</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="27">
         <v>45902</v>
       </c>
-      <c r="C8" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="29">
+      <c r="C8" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="28">
         <v>31.4</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="28">
         <v>35.4</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="28">
         <v>33.4</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="28">
+      <c r="A9" s="27">
         <v>45909</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <v>45909</v>
       </c>
-      <c r="C9" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="29">
+      <c r="C9" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="28">
         <v>31.8</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>35.799999999999997</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>33.799999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="28">
+      <c r="A10" s="27">
         <v>45916</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="27">
         <v>45916</v>
       </c>
-      <c r="C10" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="29">
+      <c r="C10" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="28">
         <v>32</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="28">
         <v>36</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="28">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="28">
+      <c r="A11" s="27">
         <v>45923</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <v>45923</v>
       </c>
-      <c r="C11" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="29">
+      <c r="C11" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="28">
         <v>32</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="28">
         <v>36</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="28">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="28">
+      <c r="A12" s="27">
         <v>45930</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="27">
         <v>45930</v>
       </c>
-      <c r="C12" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="29">
+      <c r="C12" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="28">
         <v>32</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="28">
         <v>36</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="28">
         <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="28">
+      <c r="A13" s="27">
         <v>45944</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="27">
         <v>45944</v>
       </c>
-      <c r="C13" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="29">
+      <c r="C13" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="28">
         <v>38.6</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="28">
         <v>42.6</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="28">
         <v>40.6</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="28">
+      <c r="A14" s="27">
         <v>45951</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <v>45951</v>
       </c>
-      <c r="C14" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="29">
+      <c r="C14" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="28">
         <v>38.6</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="28">
         <v>42.6</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="28">
         <v>40.6</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="28">
+      <c r="A15" s="27">
         <v>45958</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="27">
         <v>45958</v>
       </c>
-      <c r="C15" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="29">
+      <c r="C15" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="28">
         <v>38.6</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="28">
         <v>42.6</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="28">
         <v>40.6</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="28">
+      <c r="A16" s="27">
         <v>45965</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <v>45965</v>
       </c>
-      <c r="C16" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="29">
+      <c r="C16" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="28">
         <v>38.6</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="28">
         <v>42.6</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="28">
         <v>40.6</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="28">
+      <c r="A17" s="27">
         <v>45972</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="27">
         <v>45972</v>
       </c>
-      <c r="C17" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="29">
+      <c r="C17" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="28">
         <v>38.6</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="28">
         <v>42.6</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="28">
         <v>40.6</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="28">
+      <c r="A18" s="27">
         <v>45979</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="27">
         <v>45979</v>
       </c>
-      <c r="C18" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="29">
+      <c r="C18" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="28">
         <v>38.6</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <v>42.6</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <v>40.6</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="28">
+      <c r="A19" s="27">
         <v>45986</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="27">
         <v>45986</v>
       </c>
-      <c r="C19" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="29">
+      <c r="C19" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="28">
         <v>58</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="28">
         <v>62</v>
       </c>
-      <c r="G19" s="29">
+      <c r="G19" s="28">
         <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="28">
+      <c r="A20" s="27">
         <v>45993</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="27">
         <v>45993</v>
       </c>
-      <c r="C20" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="29">
+      <c r="C20" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="28">
         <v>83</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="28">
         <v>87</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="28">
         <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="28">
+      <c r="A21" s="27">
         <v>46000</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <v>46000</v>
       </c>
-      <c r="C21" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="29">
+      <c r="C21" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="28">
         <v>108</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="28">
         <v>112</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="28">
         <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="28">
+      <c r="A22" s="27">
         <v>46007</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <v>46007</v>
       </c>
-      <c r="C22" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="29">
+      <c r="C22" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="28">
         <v>108</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="28">
         <v>112</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="28">
         <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="28">
+      <c r="A23" s="27">
         <v>46014</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="27">
         <v>46014</v>
       </c>
-      <c r="C23" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="29">
+      <c r="C23" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="28">
         <v>108</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="28">
         <v>112</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="28">
         <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="28">
+      <c r="A24" s="27">
         <v>46021</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="27">
         <v>46021</v>
       </c>
-      <c r="C24" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="29">
+      <c r="C24" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="28">
         <v>108</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="28">
         <v>112</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="28">
         <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="28">
+      <c r="A25" s="27">
         <v>46028</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="27">
         <v>46028</v>
       </c>
-      <c r="C25" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="29">
+      <c r="C25" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="28">
         <v>123</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="28">
         <v>127</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="28">
         <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="23">
+      <c r="A26" s="22">
         <v>46035</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B26" s="22">
         <v>46035</v>
       </c>
-      <c r="C26" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="29">
+      <c r="C26" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="28">
         <v>123</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="28">
         <v>127</v>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="28">
         <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="23">
+      <c r="A27" s="22">
         <v>46042</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="22">
         <v>46042</v>
       </c>
-      <c r="C27" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="29">
+      <c r="C27" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="28">
         <v>158</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="28">
         <v>162</v>
       </c>
-      <c r="G27" s="29">
+      <c r="G27" s="28">
         <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="23">
+      <c r="A28" s="22">
         <v>46049</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B28" s="22">
         <v>46049</v>
       </c>
-      <c r="C28" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="30">
+      <c r="C28" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="29">
         <v>168</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="29">
         <v>172</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="29">
         <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="23">
+      <c r="A29" s="22">
         <v>46056</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B29" s="22">
         <v>46056</v>
       </c>
-      <c r="C29" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="30">
+      <c r="C29" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="29">
         <v>168</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="29">
         <v>172</v>
       </c>
-      <c r="G29" s="30">
+      <c r="G29" s="29">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="23">
+      <c r="A30" s="22">
         <v>46063</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B30" s="22">
         <v>46063</v>
       </c>
-      <c r="C30" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="30">
+      <c r="C30" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="29">
         <v>168</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="29">
         <v>172</v>
       </c>
-      <c r="G30" s="30">
+      <c r="G30" s="29">
         <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="23">
+      <c r="A31" s="22">
         <v>46077</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="22">
         <v>46077</v>
       </c>
-      <c r="C31" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="30">
+      <c r="C31" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="29">
         <v>168</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="29">
         <v>172</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="29">
         <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="23">
+      <c r="A32" s="22">
         <v>46084</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B32" s="22">
         <v>46084</v>
       </c>
-      <c r="C32" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="30">
+      <c r="C32" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="29">
         <v>168</v>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="29">
         <v>172</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="29">
         <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="23">
+      <c r="A33" s="22">
         <v>46091</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B33" s="22">
         <v>46091</v>
       </c>
-      <c r="C33" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="30">
+      <c r="C33" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="29">
         <v>188</v>
       </c>
-      <c r="F33" s="30">
+      <c r="F33" s="29">
         <v>192</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="29">
         <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="23">
+      <c r="A34" s="22">
         <v>46098</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="22">
         <v>46098</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="23">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D34" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="30">
+      <c r="D34" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="29">
         <v>188</v>
       </c>
-      <c r="F34" s="30">
+      <c r="F34" s="29">
         <v>192</v>
       </c>
-      <c r="G34" s="30">
+      <c r="G34" s="29">
         <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="23">
+      <c r="A35" s="22">
         <v>46105</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B35" s="22">
         <v>46105</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="23">
         <v>0.45833333333333298</v>
       </c>
-      <c r="D35" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="30">
+      <c r="D35" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="29">
         <v>188</v>
       </c>
-      <c r="F35" s="30">
+      <c r="F35" s="29">
         <v>192</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="29">
         <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="23">
+      <c r="A36" s="22">
         <v>46112</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B36" s="22">
         <v>46112</v>
       </c>
-      <c r="C36" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="30">
+      <c r="C36" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="29">
         <v>168</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="29">
         <v>172</v>
       </c>
-      <c r="G36" s="30">
+      <c r="G36" s="29">
         <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="23">
+      <c r="A37" s="22">
         <v>46119</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B37" s="22">
         <v>46119</v>
       </c>
-      <c r="C37" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="30">
+      <c r="C37" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="29">
         <v>168</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="29">
         <v>172</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="29">
         <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="23">
+      <c r="A38" s="22">
         <v>46126</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="22">
         <v>46126</v>
       </c>
-      <c r="C38" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D38" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="30">
+      <c r="C38" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="29">
         <v>163</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="29">
         <v>167</v>
       </c>
-      <c r="G38" s="30">
+      <c r="G38" s="29">
         <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="23">
+      <c r="A39" s="22">
         <v>46133</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B39" s="22">
         <v>46133</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="23">
         <v>0.45833333333333098</v>
       </c>
-      <c r="D39" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="30">
+      <c r="D39" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="29">
         <v>158</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F39" s="29">
         <v>162</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G39" s="29">
         <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="23">
+      <c r="A40" s="22">
         <v>46140</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B40" s="22">
         <v>46140</v>
       </c>
-      <c r="C40" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="30">
+      <c r="C40" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="29">
         <v>153</v>
       </c>
-      <c r="F40" s="30">
+      <c r="F40" s="29">
         <v>157</v>
       </c>
-      <c r="G40" s="30">
+      <c r="G40" s="29">
         <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="23">
+      <c r="A41" s="22">
         <v>46154</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B41" s="22">
         <v>46154</v>
       </c>
-      <c r="C41" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="30">
+      <c r="C41" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="29">
         <v>148</v>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="29">
         <v>152</v>
       </c>
-      <c r="G41" s="30">
+      <c r="G41" s="29">
         <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="23">
+      <c r="A42" s="22">
         <v>46161</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B42" s="22">
         <v>46161</v>
       </c>
-      <c r="C42" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D42" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="30">
+      <c r="C42" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D42" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="29">
         <v>146</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="29">
         <v>150</v>
       </c>
-      <c r="G42" s="30">
+      <c r="G42" s="29">
         <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="23">
+      <c r="A43" s="22">
         <v>46168</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B43" s="22">
         <v>46168</v>
       </c>
-      <c r="C43" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D43" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="30">
+      <c r="C43" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D43" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="29">
         <v>146</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="29">
         <v>150</v>
       </c>
-      <c r="G43" s="30">
+      <c r="G43" s="29">
         <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="23">
+      <c r="A44" s="22">
         <v>46175</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B44" s="22">
         <v>46175</v>
       </c>
-      <c r="C44" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="30">
+      <c r="C44" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D44" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="29">
         <v>146</v>
       </c>
-      <c r="F44" s="30">
+      <c r="F44" s="29">
         <v>150</v>
       </c>
-      <c r="G44" s="30">
+      <c r="G44" s="29">
         <v>148</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="23">
+      <c r="A45" s="22">
         <v>46182</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B45" s="22">
         <v>46182</v>
       </c>
-      <c r="C45" s="24">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="30">
+      <c r="C45" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D45" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="29">
         <v>147</v>
       </c>
-      <c r="F45" s="30">
+      <c r="F45" s="29">
         <v>151</v>
       </c>
-      <c r="G45" s="30">
+      <c r="G45" s="29">
         <v>149</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="22">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="22">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D46" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="29">
+        <v>148</v>
+      </c>
+      <c r="F46" s="29">
+        <v>152</v>
+      </c>
+      <c r="G46" s="29">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="22">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="22">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D47" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="29">
+        <v>148</v>
+      </c>
+      <c r="F47" s="29">
+        <v>152</v>
+      </c>
+      <c r="G47" s="29">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="22">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="22">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="23">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="29">
+        <v>153</v>
+      </c>
+      <c r="F48" s="29">
+        <v>157</v>
+      </c>
+      <c r="G48" s="29">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -4996,7 +5414,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55494817-78A6-45DF-9F77-86066DAB20E2}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -6043,6 +6461,75 @@
         <v>153</v>
       </c>
     </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="17">
+        <v>152</v>
+      </c>
+      <c r="F46" s="17">
+        <v>157</v>
+      </c>
+      <c r="G46" s="17">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="17">
+        <v>152</v>
+      </c>
+      <c r="F47" s="17">
+        <v>157</v>
+      </c>
+      <c r="G47" s="17">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="17">
+        <v>154</v>
+      </c>
+      <c r="F48" s="17">
+        <v>159</v>
+      </c>
+      <c r="G48" s="17">
+        <v>157</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6051,7 +6538,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B6A378-E9BB-4F97-B1F3-B76BB8A3CEFF}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -7098,6 +7585,75 @@
         <v>255</v>
       </c>
     </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="11">
+        <v>254</v>
+      </c>
+      <c r="F46" s="11">
+        <v>260</v>
+      </c>
+      <c r="G46" s="11">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="11">
+        <v>254</v>
+      </c>
+      <c r="F47" s="11">
+        <v>260</v>
+      </c>
+      <c r="G47" s="11">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="11">
+        <v>254</v>
+      </c>
+      <c r="F48" s="11">
+        <v>260</v>
+      </c>
+      <c r="G48" s="11">
+        <v>257</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7106,7 +7662,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D2BE078-281B-4EE8-A7DD-0530E85C5130}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -8154,6 +8710,75 @@
         <v>265</v>
       </c>
     </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="11">
+        <v>264</v>
+      </c>
+      <c r="F46" s="11">
+        <v>270</v>
+      </c>
+      <c r="G46" s="11">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="11">
+        <v>264</v>
+      </c>
+      <c r="F47" s="11">
+        <v>270</v>
+      </c>
+      <c r="G47" s="11">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="11">
+        <v>264</v>
+      </c>
+      <c r="F48" s="11">
+        <v>270</v>
+      </c>
+      <c r="G48" s="11">
+        <v>267</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
